--- a/consent_forms/045_pet_vaccination_declaration_form--consent_forms.xlsx
+++ b/consent_forms/045_pet_vaccination_declaration_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'vaccinated',_'value':_'vaccinated'}</t>
+          <t>vaccinated</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Vaccinated', 'value': 'vaccinated'}</t>
+          <t>Vaccinated</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_vaccinated',_'value':_'not_vaccinated'}</t>
+          <t>not_vaccinated</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not vaccinated', 'value': 'not_vaccinated'}</t>
+          <t>Not vaccinated</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unknown',_'value':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unknown', 'value': 'unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rabies',_'value':_'rabies'}</t>
+          <t>rabies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rabies', 'value': 'rabies'}</t>
+          <t>Rabies</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'parvovirus',_'value':_'parvovirus'}</t>
+          <t>parvovirus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Parvovirus', 'value': 'parvovirus'}</t>
+          <t>Parvovirus</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'distemper',_'value':_'distemper'}</t>
+          <t>distemper</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Distemper', 'value': 'distemper'}</t>
+          <t>Distemper</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'up-to-date',_'value':_'up-to-date'}</t>
+          <t>up-to-date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Up-to-date', 'value': 'up-to-date'}</t>
+          <t>Up-to-date</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'out-of-date',_'value':_'out-of-date'}</t>
+          <t>out-of-date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Out-of-date', 'value': 'out-of-date'}</t>
+          <t>Out-of-date</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'never_vaccinated',_'value':_'never_vaccinated'}</t>
+          <t>never_vaccinated</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Never vaccinated', 'value': 'never_vaccinated'}</t>
+          <t>Never vaccinated</t>
         </is>
       </c>
     </row>
